--- a/Data/g17.2.xlsx
+++ b/Data/g17.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +583,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nordeste</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="12">
@@ -603,11 +603,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="13">
@@ -618,11 +618,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="14">
@@ -633,11 +633,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -648,11 +648,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -663,11 +663,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="17">
@@ -678,11 +678,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="18">
@@ -693,11 +693,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2022</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="19">
@@ -708,41 +708,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sergipe</t>
+          <t>Nordeste</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -753,11 +753,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01/01/2016</t>
+          <t>01/01/2005</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.300000000000001</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="23">
@@ -768,11 +768,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>01/01/2006</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="24">
@@ -783,11 +783,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01/01/2018</t>
+          <t>01/01/2016</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -798,11 +798,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01/01/2019</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="26">
@@ -813,11 +813,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01/01/2022</t>
+          <t>01/01/2018</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="27">
@@ -828,11 +828,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01/01/2023</t>
+          <t>01/01/2019</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="28">
@@ -843,11 +843,56 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>01/01/2022</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C30" t="n">
         <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
